--- a/GATEWAY/A1#111#CGMX1/COMPUGROUP_MEDICAL_ITALIA_S.R.L/PHRONESIS/4.50/report-checklist.xlsx
+++ b/GATEWAY/A1#111#CGMX1/COMPUGROUP_MEDICAL_ITALIA_S.R.L/PHRONESIS/4.50/report-checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Domenico.DePinto\Documents\Documenti Vari\collaudi\validazione sogei 1.5 2025-2026\PHRONESIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15A4211-E1CF-46EC-8748-5B87115B91DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456BCEEB-4776-40A0-8A64-0F6E429918AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="468">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -11119,9 +11119,7 @@
       <c r="J193" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="K193" s="38" t="s">
-        <v>58</v>
-      </c>
+      <c r="K193" s="38"/>
       <c r="L193" s="38"/>
       <c r="M193" s="38"/>
       <c r="N193" s="38"/>
@@ -17382,21 +17380,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE9A258ADBC3EC4CBEB1E2AB9909207A" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0284f501378927579289f00316ec8a74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="295b7897-c886-40bf-9750-5782b814c3e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b47213d65be806e283915cff374a7eef" ns2:_="">
     <xsd:import namespace="295b7897-c886-40bf-9750-5782b814c3e4"/>
@@ -17540,24 +17523,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17575,6 +17556,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>
